--- a/docs/portfolio/evidencias-producao/exports/composicao-06001-26.xlsx
+++ b/docs/portfolio/evidencias-producao/exports/composicao-06001-26.xlsx
@@ -417,10 +417,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O32"/>
+  <dimension ref="A1:O33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="1" max="1"/>
     <col width="48" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
@@ -428,9 +428,9 @@
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="19" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
     <col width="50" customWidth="1" min="10" max="10"/>
-    <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="50" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="50" customWidth="1" min="13" max="13"/>
     <col width="50" customWidth="1" min="14" max="14"/>
@@ -1015,112 +1015,555 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sugestão de item</t>
+          <t>Composição aprovada</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Canaletas</t>
+          <t>Acessórios</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Canaleta</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+          <t>Terminais</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>MOTOR BOMBA PILOTO</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Motor</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>1.00 CV</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>19270</t>
+          <t>TE.IS.AZ.0025.08</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>DND30030 660, CANALETA (RECORTE ABERTO), 30X30MM (ALTURA X BASE), PVC RIGIDO, AZUL PETROLEO, BASE PERFURADA/DIN</t>
+          <t>TERMINAL TUBOLAR SIMPLES AZUL 2,5 MM C8 - 100 PC - E2508 BLUE -</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Elesys</t>
+          <t>E2E INDUSTRIA E COMERCIO DE COMPONENTES LTDA</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.12</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>[STATUS_APROVACAO] Sugerido pelo sistema e aprovado por DemoPac</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>[MECANICA - CANALETAS]
-Canaletas verticais: 2 | total 0 mm
-Canaletas horizontais: 2 | total 120 mm
-Comprimento total: 120 mm
-Quantidade sugerida: 0.12 m
-Origem: layout_placa do dimensionamento mecânico.</t>
+          <t>[ACESSORIO CABO - TERMINAL TUBULAR]
+Condutor: fase/comando/sinal
+Quantidade de cabos/condutores: 3
+Terminais por cabo: 2 (um por ponta)
+Quantidade sugerida: 6
+Seção efetiva: 1.50 mm2
+Tipo terminal: TUBULAR</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Aguardando aprovação</t>
+          <t>Sugerido pelo sistema e aprovado por DemoPac</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Pendência (catálogo)</t>
+          <t>Composição aprovada</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>Acessórios</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Cabo</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>W0107-PT</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>CABO FLEXIVEL 750V 2,5MM2 - PRETO</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>ELETROCAL INDUSTRIA E COMERCIO DE MATERIAIS ELETRICOS LTDA</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>[STATUS_APROVACAO] Sugerido pelo sistema e aprovado por DemoPac</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>[ACESSORIO CABO - CABO]
+Condutor: fase/polos ativos
+Quantidade de condutores: 3
+Comprimento estimado por condutor: 0.35 m
+Quantidade sugerida: 1.05 m
+Seção efetiva: 2.50 mm2
+Tipo cabo: POTENCIA
+Cor cabo: Preto
+Critério v1: comprimento de cada condutor igual à altura do painel.</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Sugerido pelo sistema e aprovado por DemoPac</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Composição aprovada</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Acessórios</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Cabo</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>MOTOR BOMBA PILOTO</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Motor</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>1.00 CV</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>W0506-VD/AM</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>CABO FLEXIVEL 750V 1,5MM2 - VERDE/AMARELO</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>ELETROCAL INDUSTRIA E COMERCIO DE MATERIAIS ELETRICOS LTDA</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>0.35</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>[STATUS_APROVACAO] Sugerido pelo sistema e aprovado por DemoPac</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>[ACESSORIO CABO - CABO]
+Condutor: PE/terra
+Quantidade de condutores: 1
+Comprimento estimado por condutor: 0.35 m
+Quantidade sugerida: 0.35 m
+Seção efetiva: 1.50 mm2
+Tipo cabo: ATERRAMENTO
+Cor cabo: Verde/Amarelo
+Critério v1: comprimento de cada condutor igual à altura do painel.</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Sugerido pelo sistema e aprovado por DemoPac</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Composição aprovada</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
           <t>Identificação</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Identificação</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>SLZ 2/15, SUPORTE LUVA TRANSPARENTE PARA FIOS E CABOS DE 2,5 A 6,0 MM², COMPRIMENTO DE 15 MM, DIAMETRO DE 3,4 A 4,5 MM</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Elesys</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>[STATUS_APROVACAO] Sugerido pelo sistema e aprovado por DemoPac</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>[ACESSORIO CABO - SUPORTE LUVA]
+Condutor: fase/polos ativos
+Quantidade de cabos/condutores: 3
+Quantidade sugerida: 3
+Seção efetiva: 2.50 mm2
+Tipo identificação: SUPORTE_LUVA_CABO</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Sugerido pelo sistema e aprovado por DemoPac</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Composição aprovada</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Acessórios</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Cabo</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>W0107-AZ</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>CABO FLEXIVEL 750V 2,5MM2 - AZUL</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>ELETROCAL INDUSTRIA E COMERCIO DE MATERIAIS ELETRICOS LTDA</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>0.35</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>[STATUS_APROVACAO] Sugerido pelo sistema e aprovado por DemoPac</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>[ACESSORIO CABO - CABO]
+Condutor: neutro
+Quantidade de condutores: 1
+Comprimento estimado por condutor: 0.35 m
+Quantidade sugerida: 0.35 m
+Seção efetiva: 2.50 mm2
+Tipo cabo: POTENCIA
+Cor cabo: Azul
+Critério v1: comprimento de cada condutor igual à altura do painel.</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Sugerido pelo sistema e aprovado por DemoPac</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Composição aprovada</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Identificação</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Identificação</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>MOTOR BOMBA PILOTO</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>Motor</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>1.00 CV</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>1.55</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Nenhuma etiqueta de identificação de cabo cadastrada.</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>326</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>SLZ 1/15, SUPORTE LUVA TRANSPARENTE PARA FIOS E CABOS DE 0,75 A 1,5 MM², COMPRIMENTO DE 15 MM, DIAMETRO DE 2,3 A 2,9 MM</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Elesys</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>[STATUS_APROVACAO] Sugerido pelo sistema e aprovado por DemoPac</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>[ACESSORIO CABO - SUPORTE LUVA]
+Condutor: fase/comando/sinal
+Quantidade de cabos/condutores: 3
+Quantidade sugerida: 3
+Seção efetiva: 1.50 mm2
+Tipo identificação: SUPORTE_LUVA_CABO</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Sugerido pelo sistema e aprovado por DemoPac</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Composição aprovada</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Acessórios</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Terminais</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>TE.IS.AZ.0025.08</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>TERMINAL TUBOLAR SIMPLES AZUL 2,5 MM C8 - 100 PC - E2508 BLUE -</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>E2E INDUSTRIA E COMERCIO DE COMPONENTES LTDA</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>[STATUS_APROVACAO] Sugerido pelo sistema e aprovado por DemoPac</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>[ACESSORIO CABO - TERMINAL TUBULAR]
+Condutor: neutro
+Quantidade de cabos/condutores: 1
+Terminais por cabo: 2 (um por ponta)
+Quantidade sugerida: 2
+Seção efetiva: 2.50 mm2
+Tipo terminal: TUBULAR</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Sugerido pelo sistema e aprovado por DemoPac</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Composição aprovada</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Identificação</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Identificação</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>359</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>ETA 7X15 960 211, ETIQUETA PARA APARELHOS, CANTO ARREDONDADO, 7X15 MM, BRANCO, PVC FLEXIVEL ADESIVO, 7500 ETIQUETAS</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Elesys</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>[STATUS_APROVACAO] Sugerido pelo sistema e aprovado por DemoPac</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
         <is>
           <t>[ACESSORIO CABO - ETIQUETA]
 Condutor: PE/terra
@@ -1129,43 +1572,497 @@
 Tipo identificação: ETIQUETA_CABO</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>Aberta</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Pendência (catálogo)</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Sugerido pelo sistema e aprovado por DemoPac</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Composição aprovada</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
         <is>
           <t>Identificação</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Identificação</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Nenhum suporte/luva de cabo compatível com a seção 2.50 mm2 para neutro.</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>SLZ 2/15, SUPORTE LUVA TRANSPARENTE PARA FIOS E CABOS DE 2,5 A 6,0 MM², COMPRIMENTO DE 15 MM, DIAMETRO DE 3,4 A 4,5 MM</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Elesys</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>[STATUS_APROVACAO] Sugerido pelo sistema e aprovado por DemoPac</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>[ACESSORIO CABO - SUPORTE LUVA]
+Condutor: PE/terra
+Quantidade de cabos/condutores: 1
+Quantidade sugerida: 1
+Seção efetiva: 2.50 mm2
+Tipo identificação: SUPORTE_LUVA_CABO</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Sugerido pelo sistema e aprovado por DemoPac</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Composição aprovada</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Acessórios</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Cabo</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>W0507-VD/AM</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>CABO FLEXIVEL 750V 2,5MM2 - VERDE/AMARELO</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>ELETROCAL INDUSTRIA E COMERCIO DE MATERIAIS ELETRICOS LTDA</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>0.35</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>[STATUS_APROVACAO] Sugerido pelo sistema e aprovado por DemoPac</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>[ACESSORIO CABO - CABO]
+Condutor: PE/terra
+Quantidade de condutores: 1
+Comprimento estimado por condutor: 0.35 m
+Quantidade sugerida: 0.35 m
+Seção efetiva: 2.50 mm2
+Tipo cabo: ATERRAMENTO
+Cor cabo: Verde/Amarelo
+Critério v1: comprimento de cada condutor igual à altura do painel.</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Sugerido pelo sistema e aprovado por DemoPac</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Composição aprovada</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Identificação</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Identificação</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>MOTOR BOMBA PILOTO</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Motor</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>1.00 CV</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>326</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>SLZ 1/15, SUPORTE LUVA TRANSPARENTE PARA FIOS E CABOS DE 0,75 A 1,5 MM², COMPRIMENTO DE 15 MM, DIAMETRO DE 2,3 A 2,9 MM</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Elesys</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>[STATUS_APROVACAO] Sugerido pelo sistema e aprovado por DemoPac</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>[ACESSORIO CABO - SUPORTE LUVA]
+Condutor: PE/terra
+Quantidade de cabos/condutores: 1
+Quantidade sugerida: 1
+Seção efetiva: 1.50 mm2
+Tipo identificação: SUPORTE_LUVA_CABO</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Sugerido pelo sistema e aprovado por DemoPac</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Composição aprovada</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Acessórios</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Terminais</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>TE.IS.AZ.0025.08</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>TERMINAL TUBOLAR SIMPLES AZUL 2,5 MM C8 - 100 PC - E2508 BLUE -</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>E2E INDUSTRIA E COMERCIO DE COMPONENTES LTDA</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>[STATUS_APROVACAO] Sugerido pelo sistema e aprovado por DemoPac</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>[ACESSORIO CABO - TERMINAL TUBULAR]
+Condutor: PE/terra
+Quantidade de cabos/condutores: 1
+Terminais por cabo: 2 (um por ponta)
+Quantidade sugerida: 2
+Seção efetiva: 2.50 mm2
+Tipo terminal: TUBULAR</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Sugerido pelo sistema e aprovado por DemoPac</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Composição aprovada</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Acessórios</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Cabo</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>MOTOR BOMBA PILOTO</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Motor</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>1.00 CV</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>W0106-PT</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>CABO FLEXIVEL 750V 1,5MM2 - PRETO</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>ELETROCAL INDUSTRIA E COMERCIO DE MATERIAIS ELETRICOS LTDA</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>[STATUS_APROVACAO] Sugerido pelo sistema e aprovado por DemoPac</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>[ACESSORIO CABO - CABO]
+Condutor: fase/comando/sinal
+Quantidade de condutores: 3
+Comprimento estimado por condutor: 0.35 m
+Quantidade sugerida: 1.05 m
+Seção efetiva: 1.50 mm2
+Tipo cabo: POTENCIA
+Cor cabo: Preto
+Critério v1: comprimento de cada condutor igual à altura do painel.</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Sugerido pelo sistema e aprovado por DemoPac</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Composição aprovada</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Identificação</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Identificação</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>MOTOR BOMBA PILOTO</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Motor</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>1.00 CV</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>359</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>ETA 7X15 960 211, ETIQUETA PARA APARELHOS, CANTO ARREDONDADO, 7X15 MM, BRANCO, PVC FLEXIVEL ADESIVO, 7500 ETIQUETAS</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Elesys</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>[STATUS_APROVACAO] Sugerido pelo sistema e aprovado por DemoPac</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>[ACESSORIO CABO - ETIQUETA]
+Condutor: PE/terra
+Quantidade de cabos/condutores: 1
+Quantidade sugerida: 1
+Tipo identificação: ETIQUETA_CABO</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Sugerido pelo sistema e aprovado por DemoPac</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Composição aprovada</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Identificação</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Identificação</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>SLZ 2/15, SUPORTE LUVA TRANSPARENTE PARA FIOS E CABOS DE 2,5 A 6,0 MM², COMPRIMENTO DE 15 MM, DIAMETRO DE 3,4 A 4,5 MM</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Elesys</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>[STATUS_APROVACAO] Sugerido pelo sistema e aprovado por DemoPac</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
         <is>
           <t>[ACESSORIO CABO - SUPORTE LUVA]
 Condutor: neutro
@@ -1175,112 +2072,140 @@
 Tipo identificação: SUPORTE_LUVA_CABO</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>Aberta</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Pendência (catálogo)</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Acessórios</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Cabo</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Sugerido pelo sistema e aprovado por DemoPac</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Composição aprovada</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Identificação</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Identificação</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>MOTOR BOMBA PILOTO</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>Motor</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>1.00 CV</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>1.55</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Nenhum cabo unipolar compatível cadastrado para fase/comando/sinal, tipo POTENCIA, cor Preto, seção 1.50 mm2, ou a altura do painel ainda não foi definida no dimensionamento mecânico.</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>[ACESSORIO CABO - CABO]
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>359</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>ETA 7X15 960 211, ETIQUETA PARA APARELHOS, CANTO ARREDONDADO, 7X15 MM, BRANCO, PVC FLEXIVEL ADESIVO, 7500 ETIQUETAS</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Elesys</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>[STATUS_APROVACAO] Sugerido pelo sistema e aprovado por DemoPac</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>[ACESSORIO CABO - ETIQUETA]
 Condutor: fase/comando/sinal
-Quantidade de condutores: 3
-Comprimento estimado por condutor: 0.10 m
-Quantidade sugerida: 0.30 m
-Seção efetiva: 1.50 mm2
-Tipo cabo: POTENCIA
-Cor cabo: Preto
-Critério v1: comprimento de cada condutor igual à altura do painel.</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>Aberta</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Pendência (catálogo)</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
+Quantidade de cabos/condutores: 3
+Quantidade sugerida: 3
+Tipo identificação: ETIQUETA_CABO</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Sugerido pelo sistema e aprovado por DemoPac</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Composição aprovada</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
         <is>
           <t>Identificação</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>Identificação</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Nenhuma etiqueta de identificação de cabo cadastrada.</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>359</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>ETA 7X15 960 211, ETIQUETA PARA APARELHOS, CANTO ARREDONDADO, 7X15 MM, BRANCO, PVC FLEXIVEL ADESIVO, 7500 ETIQUETAS</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Elesys</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>[STATUS_APROVACAO] Sugerido pelo sistema e aprovado por DemoPac</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
         <is>
           <t>[ACESSORIO CABO - ETIQUETA]
 Condutor: fase/polos ativos
@@ -1289,224 +2214,203 @@
 Tipo identificação: ETIQUETA_CABO</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>Aberta</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Pendência (catálogo)</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Sugerido pelo sistema e aprovado por DemoPac</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Composição aprovada</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
         <is>
           <t>Acessórios</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Cabo</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Terminais</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>MOTOR BOMBA PILOTO</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>Motor</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>1.00 CV</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>1.55</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Nenhum cabo unipolar compatível cadastrado para PE/terra, tipo ATERRAMENTO, cor Verde/Amarelo, seção 1.50 mm2, ou a altura do painel ainda não foi definida no dimensionamento mecânico.</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>[ACESSORIO CABO - CABO]
-Condutor: PE/terra
-Quantidade de condutores: 1
-Comprimento estimado por condutor: 0.10 m
-Quantidade sugerida: 0.10 m
-Seção efetiva: 1.50 mm2
-Tipo cabo: ATERRAMENTO
-Cor cabo: Verde/Amarelo
-Critério v1: comprimento de cada condutor igual à altura do painel.</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>Aberta</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Pendência (catálogo)</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Identificação</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Identificação</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Nenhum suporte/luva de cabo compatível com a seção 2.50 mm2 para PE/terra.</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>[ACESSORIO CABO - SUPORTE LUVA]
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>TE.IS.AZ.0025.08</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>TERMINAL TUBOLAR SIMPLES AZUL 2,5 MM C8 - 100 PC - E2508 BLUE -</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>E2E INDUSTRIA E COMERCIO DE COMPONENTES LTDA</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>[STATUS_APROVACAO] Sugerido pelo sistema e aprovado por DemoPac</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>[ACESSORIO CABO - TERMINAL TUBULAR]
 Condutor: PE/terra
 Quantidade de cabos/condutores: 1
-Quantidade sugerida: 1
-Seção efetiva: 2.50 mm2
-Tipo identificação: SUPORTE_LUVA_CABO</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>Aberta</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Pendência (catálogo)</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
+Terminais por cabo: 2 (um por ponta)
+Quantidade sugerida: 2
+Seção efetiva: 1.50 mm2
+Tipo terminal: TUBULAR</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Sugerido pelo sistema e aprovado por DemoPac</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Composição aprovada</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
         <is>
           <t>Identificação</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>Identificação</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>M1</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>MOTOR BOMBA PILOTO</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Motor</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>1.00 CV</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Nenhum suporte/luva de cabo compatível com a seção 1.50 mm2 para PE/terra.</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>[ACESSORIO CABO - SUPORTE LUVA]
-Condutor: PE/terra
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>359</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>ETA 7X15 960 211, ETIQUETA PARA APARELHOS, CANTO ARREDONDADO, 7X15 MM, BRANCO, PVC FLEXIVEL ADESIVO, 7500 ETIQUETAS</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Elesys</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>[STATUS_APROVACAO] Sugerido pelo sistema e aprovado por DemoPac</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>[ACESSORIO CABO - ETIQUETA]
+Condutor: neutro
 Quantidade de cabos/condutores: 1
 Quantidade sugerida: 1
-Seção efetiva: 1.50 mm2
-Tipo identificação: SUPORTE_LUVA_CABO</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>Aberta</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Pendência (catálogo)</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
+Tipo identificação: ETIQUETA_CABO</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Sugerido pelo sistema e aprovado por DemoPac</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Composição aprovada</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
         <is>
           <t>Acessórios</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>Terminais</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Nenhum terminal tubular compatível com a seção 2.50 mm2 para fase/polos ativos.</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>TE.IS.AZ.0025.08</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>TERMINAL TUBOLAR SIMPLES AZUL 2,5 MM C8 - 100 PC - E2508 BLUE -</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>E2E INDUSTRIA E COMERCIO DE COMPONENTES LTDA</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>[STATUS_APROVACAO] Sugerido pelo sistema e aprovado por DemoPac</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
         <is>
           <t>[ACESSORIO CABO - TERMINAL TUBULAR]
 Condutor: fase/polos ativos
@@ -1517,621 +2421,26 @@
 Tipo terminal: TUBULAR</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>Aberta</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Pendência (catálogo)</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Acessórios</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Terminais</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>M1</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>MOTOR BOMBA PILOTO</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Motor</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>1.00 CV</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>Nenhum terminal tubular compatível com a seção 1.50 mm2 para PE/terra.</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>[ACESSORIO CABO - TERMINAL TUBULAR]
-Condutor: PE/terra
-Quantidade de cabos/condutores: 1
-Terminais por cabo: 2 (um por ponta)
-Quantidade sugerida: 2
-Seção efetiva: 1.50 mm2
-Tipo terminal: TUBULAR</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>Aberta</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Pendência (catálogo)</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Acessórios</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Cabo</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Nenhum cabo unipolar compatível cadastrado para PE/terra, tipo ATERRAMENTO, cor Verde/Amarelo, seção 2.50 mm2, ou a altura do painel ainda não foi definida no dimensionamento mecânico.</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>[ACESSORIO CABO - CABO]
-Condutor: PE/terra
-Quantidade de condutores: 1
-Comprimento estimado por condutor: 0.10 m
-Quantidade sugerida: 0.10 m
-Seção efetiva: 2.50 mm2
-Tipo cabo: ATERRAMENTO
-Cor cabo: Verde/Amarelo
-Critério v1: comprimento de cada condutor igual à altura do painel.</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>Aberta</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Pendência (catálogo)</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Acessórios</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Terminais</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>M1</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>MOTOR BOMBA PILOTO</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Motor</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>1.00 CV</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>Nenhum terminal tubular compatível com a seção 1.50 mm2 para fase/comando/sinal.</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>[ACESSORIO CABO - TERMINAL TUBULAR]
-Condutor: fase/comando/sinal
-Quantidade de cabos/condutores: 3
-Terminais por cabo: 2 (um por ponta)
-Quantidade sugerida: 6
-Seção efetiva: 1.50 mm2
-Tipo terminal: TUBULAR</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>Aberta</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Pendência (catálogo)</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Identificação</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Identificação</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>Nenhum suporte/luva de cabo compatível com a seção 2.50 mm2 para fase/polos ativos.</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>[ACESSORIO CABO - SUPORTE LUVA]
-Condutor: fase/polos ativos
-Quantidade de cabos/condutores: 3
-Quantidade sugerida: 3
-Seção efetiva: 2.50 mm2
-Tipo identificação: SUPORTE_LUVA_CABO</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>Aberta</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Pendência (catálogo)</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Identificação</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Identificação</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>M1</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>MOTOR BOMBA PILOTO</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Motor</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>1.00 CV</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>Nenhum suporte/luva de cabo compatível com a seção 1.50 mm2 para fase/comando/sinal.</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>[ACESSORIO CABO - SUPORTE LUVA]
-Condutor: fase/comando/sinal
-Quantidade de cabos/condutores: 3
-Quantidade sugerida: 3
-Seção efetiva: 1.50 mm2
-Tipo identificação: SUPORTE_LUVA_CABO</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>Aberta</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Pendência (catálogo)</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Acessórios</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Cabo</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>Nenhum cabo unipolar compatível cadastrado para neutro, tipo POTENCIA, cor Azul, seção 2.50 mm2, ou a altura do painel ainda não foi definida no dimensionamento mecânico.</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>[ACESSORIO CABO - CABO]
-Condutor: neutro
-Quantidade de condutores: 1
-Comprimento estimado por condutor: 0.10 m
-Quantidade sugerida: 0.10 m
-Seção efetiva: 2.50 mm2
-Tipo cabo: POTENCIA
-Cor cabo: Azul
-Critério v1: comprimento de cada condutor igual à altura do painel.</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>Aberta</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Pendência (catálogo)</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Identificação</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Identificação</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>Nenhuma etiqueta de identificação de cabo cadastrada.</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>[ACESSORIO CABO - ETIQUETA]
-Condutor: PE/terra
-Quantidade de cabos/condutores: 1
-Quantidade sugerida: 1
-Tipo identificação: ETIQUETA_CABO</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>Aberta</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Pendência (catálogo)</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Acessórios</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Terminais</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>Nenhum terminal tubular compatível com a seção 2.50 mm2 para PE/terra.</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>[ACESSORIO CABO - TERMINAL TUBULAR]
-Condutor: PE/terra
-Quantidade de cabos/condutores: 1
-Terminais por cabo: 2 (um por ponta)
-Quantidade sugerida: 2
-Seção efetiva: 2.50 mm2
-Tipo terminal: TUBULAR</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>Aberta</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Pendência (catálogo)</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Identificação</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Identificação</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>Nenhuma etiqueta de identificação de cabo cadastrada.</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>[ACESSORIO CABO - ETIQUETA]
-Condutor: neutro
-Quantidade de cabos/condutores: 1
-Quantidade sugerida: 1
-Tipo identificação: ETIQUETA_CABO</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>Aberta</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Pendência (catálogo)</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Acessórios</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Cabo</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>Nenhum cabo unipolar compatível cadastrado para fase/polos ativos, tipo POTENCIA, cor Preto, seção 2.50 mm2, ou a altura do painel ainda não foi definida no dimensionamento mecânico.</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>[ACESSORIO CABO - CABO]
-Condutor: fase/polos ativos
-Quantidade de condutores: 3
-Comprimento estimado por condutor: 0.10 m
-Quantidade sugerida: 0.30 m
-Seção efetiva: 2.50 mm2
-Tipo cabo: POTENCIA
-Cor cabo: Preto
-Critério v1: comprimento de cada condutor igual à altura do painel.</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>Aberta</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Pendência (catálogo)</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Identificação</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Identificação</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>M1</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>MOTOR BOMBA PILOTO</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Motor</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>1.00 CV</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>Nenhuma etiqueta de identificação de cabo cadastrada.</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>[ACESSORIO CABO - ETIQUETA]
-Condutor: fase/comando/sinal
-Quantidade de cabos/condutores: 3
-Quantidade sugerida: 3
-Tipo identificação: ETIQUETA_CABO</t>
-        </is>
-      </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Aberta</t>
+          <t>Sugerido pelo sistema e aprovado por DemoPac</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Pendência (catálogo)</t>
+          <t>Composição aprovada</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Acessórios</t>
+          <t>Estrutura</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Terminais</t>
+          <t>Trilho DIN</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -2139,46 +2448,60 @@
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>C038340.0000</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Nenhum terminal tubular compatível com a seção 2.50 mm2 para neutro.</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
+          <t>#TRILHO TS35 X 7,5 ACO S/FURO (C038340.0000)</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>WEIDMULLER CONEXEL DO BRASIL</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>0.58</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>[STATUS_APROVACAO] Sugerido pelo sistema e aprovado por DemoPac</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>[ACESSORIO CABO - TERMINAL TUBULAR]
-Condutor: neutro
-Quantidade de cabos/condutores: 1
-Terminais por cabo: 2 (um por ponta)
-Quantidade sugerida: 2
-Seção efetiva: 2.50 mm2
-Tipo terminal: TUBULAR</t>
+          <t>[MECANICA - TRILHOS DIN]
+Trilhos DIN: 2
+Comprimento total: 580 mm
+Quantidade sugerida: 0.58 m
+Origem: layout_placa do dimensionamento mecânico.</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Aberta</t>
+          <t>Sugerido pelo sistema e aprovado por DemoPac</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Pendência (catálogo)</t>
+          <t>Composição aprovada</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Acessórios</t>
+          <t>Canaletas</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Acessórios Gerais</t>
+          <t>Canaleta</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -2186,30 +2509,104 @@
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>19270</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Nenhum kit de acessórios gerais cadastrado para painel porte MEDIO com dimensões - x - mm.</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
+          <t>DND30030 660, CANALETA (RECORTE ABERTO), 30X30MM (ALTURA X BASE), PVC RIGIDO, AZUL PETROLEO, BASE PERFURADA/DIN</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Elesys</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>[STATUS_APROVACAO] Sugerido pelo sistema e aprovado por DemoPac</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr">
         <is>
+          <t>[MECANICA - CANALETAS]
+Canaletas verticais: 2 | total 580 mm
+Canaletas horizontais: 3 | total 990 mm
+Comprimento total: 1570 mm
+Quantidade sugerida: 1.57 m
+Origem: layout_placa do dimensionamento mecânico.</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Sugerido pelo sistema e aprovado por DemoPac</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Composição aprovada</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Acessórios</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Acessórios Gerais</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>ZFW-KIT-PAINEL_PEQUENO</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>KIT ACESSORIOS PAINEL PEQUENO</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>[STATUS_APROVACAO] Sugerido pelo sistema e aprovado por DemoPac</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
           <t>[ACESSORIOS GERAIS]
-Porte calculado: MEDIO
-Largura referência: não informada mm
-Altura referência: não informada mm
-Profundidade referência: não informada mm
+Porte calculado: PEQUENO
+Largura referência: 350.00 mm
+Altura referência: 350.00 mm
+Profundidade referência: 200.00 mm
 Tipo acessório: KIT_MONTAGEM
 Quantidade sugerida: 1.00
 Critério v1: kit de montagem por porte/faixa do painel após dimensionamento mecânico.</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>Aberta</t>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Sugerido pelo sistema e aprovado por DemoPac</t>
         </is>
       </c>
     </row>
